--- a/src/main/resources/xlsx/forbidden_pool_query_export_template.xlsx
+++ b/src/main/resources/xlsx/forbidden_pool_query_export_template.xlsx
@@ -1,43 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
-  <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
-  </bookViews>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheets>
-    <sheet name="禁投池查询" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="禁投池查询" sheetId="1" r:id="Rfe4d555e79a643f8"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
   <fonts count="3">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
       <name val="楷体"/>
-      <b val="1"/>
-      <sz val="11"/>
     </font>
     <font>
+      <sz val="11"/>
       <name val="楷体"/>
-      <sz val="11"/>
     </font>
   </fonts>
   <fills count="3">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -61,18 +57,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -308,7 +303,7 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525">
           <a:solidFill>
             <a:schemeClr val="phClr">
               <a:shade val="95000"/>
@@ -317,13 +312,13 @@
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="25400">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -357,17 +352,6 @@
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
@@ -422,137 +406,173 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
+    <col min="1" max="1" width="15" customWidth="1"/>
+    <col min="2" max="2" width="15" customWidth="1"/>
+    <col min="3" max="3" width="15" customWidth="1"/>
+    <col min="4" max="4" width="15" customWidth="1"/>
+    <col min="5" max="5" width="15" customWidth="1"/>
+    <col min="6" max="6" width="15" customWidth="1"/>
+    <col min="7" max="7" width="15" customWidth="1"/>
+    <col min="8" max="8" width="15" customWidth="1"/>
+    <col min="9" max="9" width="15" customWidth="1"/>
+    <col min="10" max="10" width="15" customWidth="1"/>
+    <col min="11" max="11" width="22" hidden="0" customWidth="1"/>
+    <col min="12" max="12" width="22" hidden="0" customWidth="1"/>
+    <col min="13" max="13" width="22" hidden="0" customWidth="1"/>
+    <col min="14" max="14" width="22" hidden="0" customWidth="1"/>
+    <col min="15" max="15" width="22" hidden="0" customWidth="1"/>
+    <col min="16" max="16" width="22" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>证券简称</t>
+          <t xml:space="preserve">证券简称</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>证券代码</t>
+          <t xml:space="preserve">证券代码</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>发行主体</t>
+          <t xml:space="preserve">发行主体</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>调整人</t>
+          <t xml:space="preserve">调整人</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>证券类型</t>
+          <t xml:space="preserve">证券类型</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>投资池名称</t>
+          <t xml:space="preserve">投资池名称</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>入池时间</t>
+          <t xml:space="preserve">入池时间</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>证券状态</t>
+          <t xml:space="preserve">证券状态</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>退市日期</t>
+          <t xml:space="preserve">退市日期</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>行权日期（回售）</t>
-        </is>
+          <t xml:space="preserve">行权日期（回售）</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="str">
+        <v>ISIN</v>
+      </c>
+      <c r="L1" s="1" t="str">
+        <v>沪市代码</v>
+      </c>
+      <c r="M1" s="1" t="str">
+        <v>深市代码</v>
+      </c>
+      <c r="N1" s="1" t="str">
+        <v>银行间代码</v>
+      </c>
+      <c r="O1" s="1" t="str">
+        <v>北交所代码</v>
+      </c>
+      <c r="P1" s="1" t="str">
+        <v>其他市场代码</v>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>{data.securityShortName}</t>
+          <t xml:space="preserve">{data.securityShortName}</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>{data.securityCode}</t>
+          <t xml:space="preserve">{data.securityCode}</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>{data.issuer}</t>
+          <t xml:space="preserve">{data.issuer}</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>{data.adjusterName}</t>
+          <t xml:space="preserve">{data.adjusterName}</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>{data.securityTypeName}</t>
+          <t xml:space="preserve">{data.securityTypeName}</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>{data.targetPoolName}</t>
+          <t xml:space="preserve">{data.targetPoolName}</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>{data.entryTime}</t>
+          <t xml:space="preserve">{data.entryTime}</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>{data.securityStatusLabel}</t>
+          <t xml:space="preserve">{data.securityStatusLabel}</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>{data.delistDate}</t>
+          <t xml:space="preserve">{data.delistDate}</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>{data.repurchaseDate}</t>
-        </is>
+          <t xml:space="preserve">{data.repurchaseDate}</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="str">
+        <v>{data.isinCode}</v>
+      </c>
+      <c r="L2" s="2" t="str">
+        <v>{data.windCodeSh}</v>
+      </c>
+      <c r="M2" s="2" t="str">
+        <v>{data.windCodeSz}</v>
+      </c>
+      <c r="N2" s="2" t="str">
+        <v>{data.windCodeNib}</v>
+      </c>
+      <c r="O2" s="2" t="str">
+        <v>{data.windCodeBj}</v>
+      </c>
+      <c r="P2" s="2" t="str">
+        <v>{data.windCodeNbc}</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/src/main/resources/xlsx/forbidden_pool_query_export_template.xlsx
+++ b/src/main/resources/xlsx/forbidden_pool_query_export_template.xlsx
@@ -1,39 +1,43 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <workbookProtection/>
+  <bookViews>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+  </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="禁投池查询" sheetId="1" r:id="Rfe4d555e79a643f8"/>
+    <sheet name="禁投池查询" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
-</file>
-
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="3">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <name val="楷体"/>
+      <b val="1"/>
       <sz val="11"/>
-      <name val="楷体"/>
     </font>
     <font>
+      <name val="楷体"/>
       <sz val="11"/>
-      <name val="楷体"/>
     </font>
   </fonts>
   <fills count="3">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -57,17 +61,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -303,7 +308,7 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr">
               <a:shade val="95000"/>
@@ -312,13 +317,13 @@
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="25400">
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="38100">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -352,6 +357,17 @@
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
@@ -406,173 +422,137 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:P2"/>
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="15" customWidth="1"/>
-    <col min="2" max="2" width="15" customWidth="1"/>
-    <col min="3" max="3" width="15" customWidth="1"/>
-    <col min="4" max="4" width="15" customWidth="1"/>
-    <col min="5" max="5" width="15" customWidth="1"/>
-    <col min="6" max="6" width="15" customWidth="1"/>
-    <col min="7" max="7" width="15" customWidth="1"/>
-    <col min="8" max="8" width="15" customWidth="1"/>
-    <col min="9" max="9" width="15" customWidth="1"/>
-    <col min="10" max="10" width="15" customWidth="1"/>
-    <col min="11" max="11" width="22" hidden="0" customWidth="1"/>
-    <col min="12" max="12" width="22" hidden="0" customWidth="1"/>
-    <col min="13" max="13" width="22" hidden="0" customWidth="1"/>
-    <col min="14" max="14" width="22" hidden="0" customWidth="1"/>
-    <col min="15" max="15" width="22" hidden="0" customWidth="1"/>
-    <col min="16" max="16" width="22" hidden="0" customWidth="1"/>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">证券简称</t>
+          <t>证券简称</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">证券代码</t>
+          <t>证券代码</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">发行主体</t>
+          <t>发行主体</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">调整人</t>
+          <t>调整人</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">证券类型</t>
+          <t>证券类型</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">投资池名称</t>
+          <t>投资池名称</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">入池时间</t>
+          <t>入池时间</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">证券状态</t>
+          <t>证券状态</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">退市日期</t>
+          <t>退市日期</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">行权日期（回售）</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="str">
-        <v>ISIN</v>
-      </c>
-      <c r="L1" s="1" t="str">
-        <v>沪市代码</v>
-      </c>
-      <c r="M1" s="1" t="str">
-        <v>深市代码</v>
-      </c>
-      <c r="N1" s="1" t="str">
-        <v>银行间代码</v>
-      </c>
-      <c r="O1" s="1" t="str">
-        <v>北交所代码</v>
-      </c>
-      <c r="P1" s="1" t="str">
-        <v>其他市场代码</v>
+          <t>行权日期（回售）</t>
+        </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">{data.securityShortName}</t>
+          <t>{data.securityShortName}</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">{data.securityCode}</t>
+          <t>{data.securityCode}</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">{data.issuer}</t>
+          <t>{data.issuer}</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">{data.adjusterName}</t>
+          <t>{data.adjusterName}</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">{data.securityTypeName}</t>
+          <t>{data.securityTypeName}</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">{data.targetPoolName}</t>
+          <t>{data.targetPoolName}</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">{data.entryTime}</t>
+          <t>{data.entryTime}</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">{data.securityStatusLabel}</t>
+          <t>{data.securityStatusLabel}</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">{data.delistDate}</t>
+          <t>{data.delistDate}</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">{data.repurchaseDate}</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="str">
-        <v>{data.isinCode}</v>
-      </c>
-      <c r="L2" s="2" t="str">
-        <v>{data.windCodeSh}</v>
-      </c>
-      <c r="M2" s="2" t="str">
-        <v>{data.windCodeSz}</v>
-      </c>
-      <c r="N2" s="2" t="str">
-        <v>{data.windCodeNib}</v>
-      </c>
-      <c r="O2" s="2" t="str">
-        <v>{data.windCodeBj}</v>
-      </c>
-      <c r="P2" s="2" t="str">
-        <v>{data.windCodeNbc}</v>
+          <t>{data.repurchaseDate}</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>